--- a/docs/02_基本設計/05_権限・メッセージ・帳票/KF-BD-006_メッセージ一覧.xlsx
+++ b/docs/02_基本設計/05_権限・メッセージ・帳票/KF-BD-006_メッセージ一覧.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D10" s="10" t="n"/>
@@ -631,6 +631,8 @@
       </c>
       <c r="D12" s="10" t="n"/>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -677,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -782,6 +784,29 @@
         </is>
       </c>
       <c r="E4" s="11" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>2026/10/04</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>E-017（アカウントロック・HTTP 423）、E-018（現在のパスワード不一致）、I-008（パスワード変更完了）を追加。E-002 にパスワードポリシー違反時の文言を追記（SCR-001 ログイン堅牢化 / SCR-007 パスワード変更 / ONL-023）</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -795,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -811,6 +836,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -868,12 +894,12 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>{項目名}は必須入力です。</t>
+          <t>{項目名}は必須入力です。／新しいパスワードのポリシー違反時はポリシー別の文言（12文字以上、英字と数字を両方含む、現在のパスワードと異なる）</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>全画面</t>
+          <t>全画面，SCR-007（パスワードポリシー違反）</t>
         </is>
       </c>
     </row>
@@ -1188,95 +1214,95 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>W-001</t>
+          <t>E-017</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>確認</t>
+          <t>エラー</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>申請を提出します。よろしいですか。</t>
+          <t>アカウントがロックされています。しばらくしてから再度お試しください。（HTTP 423。ログイン失敗が 5 回続くと 30 分ロック）</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>SCR-104, SCR-105, SCR-106</t>
+          <t>SCR-001</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>W-002</t>
+          <t>E-018</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>確認</t>
+          <t>エラー</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>申請を取り下げます。よろしいですか。</t>
+          <t>現在のパスワードが正しくありません。（HTTP 400）</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>SCR-106</t>
+          <t>SCR-007</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>I-001</t>
+          <t>W-001</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>情報</t>
+          <t>確認</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>出勤を記録しました。</t>
+          <t>申請を提出します。よろしいですか。</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>SCR-102</t>
+          <t>SCR-104, SCR-105, SCR-106</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>I-002</t>
+          <t>W-002</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>情報</t>
+          <t>確認</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>退勤を記録しました。</t>
+          <t>申請を取り下げます。よろしいですか。</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>SCR-102</t>
+          <t>SCR-106</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>I-003</t>
+          <t>I-001</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
@@ -1286,19 +1312,19 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>申請を提出しました。</t>
+          <t>出勤を記録しました。</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>SCR-104, SCR-105, SCR-106</t>
+          <t>SCR-102</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>I-004</t>
+          <t>I-002</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
@@ -1308,19 +1334,19 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>承認しました。</t>
+          <t>退勤を記録しました。</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>SCR-202</t>
+          <t>SCR-102</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>I-005</t>
+          <t>I-003</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
@@ -1330,19 +1356,19 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>差戻ししました。</t>
+          <t>申請を提出しました。</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>SCR-202</t>
+          <t>SCR-104, SCR-105, SCR-106</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>I-006</t>
+          <t>I-004</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
@@ -1352,7 +1378,7 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>却下しました。</t>
+          <t>承認しました。</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -1364,22 +1390,88 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
+          <t>I-005</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>情報</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>差戻ししました。</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>SCR-202</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>I-006</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>情報</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>却下しました。</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>SCR-202</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
           <t>I-007</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>情報</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>申請を取り下げました。</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>SCR-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>I-008</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>情報</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>パスワードを変更しました。</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>SCR-007</t>
         </is>
       </c>
     </row>

--- a/docs/02_基本設計/05_権限・メッセージ・帳票/KF-BD-006_メッセージ一覧.xlsx
+++ b/docs/02_基本設計/05_権限・メッセージ・帳票/KF-BD-006_メッセージ一覧.xlsx
@@ -10,6 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表紙" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改訂履歴" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="メッセージ一覧" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入力チェックメッセージ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画面側メッセージ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -78,7 +80,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -147,11 +149,17 @@
         <color rgb="00999999"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -174,6 +182,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -600,7 +614,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D10" s="10" t="n"/>
@@ -679,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -807,6 +821,52 @@
         </is>
       </c>
       <c r="E5" s="11" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>実装（BusinessException・GlobalExceptionHandler・SecurityConfig・Bean Validation）と照合。E-019（HTTP 403・要パスワード変更）を追加。全エラーに HTTP ステータス・発生条件列を追加し、E-001（401 の実装文言）・E-003・E-013〜E-016 の文言・項目名を実装に合わせて修正。W-002〜W-007・I-001〜I-012（実装の確認・完了メッセージ）を更新。入力チェックメッセージ・画面側メッセージのシートを追加</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>休憩・離席の打刻・修正に伴い E-020（既に休憩中または離席中）・E-021（休憩中・離席中ではない）・E-022（休憩中・離席中は退勤不可）を追加（いずれも HTTP 409）。E-003 に休憩・離席修正の 3 文言、E-005 に区間重複の文言、E-007 に休憩・離席の打刻時の文言を追記。I-013・I-014（休憩・離席の開始・終了完了）を追加。入力チェックに break-start の kind・休憩離席修正（breakKind / breakStart / breakEnd）を追加し、管理者が設定する初期・再設定パスワードのメッセージを「12文字以上72文字以内」・英字と数字の両方を含む検査に修正。画面側メッセージを打刻修正の出勤・退勤の両方必須に合わせて修正</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -820,42 +880,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="64" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="72" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>※E：エラー　W：確認　I：情報。{ }内は実行時に置き換える。</t>
+          <t>※E：エラー　W：確認　I：情報。{ }内は実行時に置き換える。エラーは API が返す code / message（実装の BusinessException・GlobalExceptionHandler・SecurityConfig）と一致させる。HTTP は実装のステータス。</t>
         </is>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>メッセージID</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>メッセージ</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>主な発生画面</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>発生条件・備考</t>
         </is>
       </c>
     </row>
@@ -872,12 +944,22 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>メールアドレスまたはパスワードが正しくありません。（ログイン時）／認証情報が無効、または有効期限が切れています。再度ログインしてください。（トークンなし・不正・期限切れ。HTTP 401）</t>
+          <t>メールアドレスまたはパスワードが正しくありません。（ログイン時）／認証が必要です。再度ログインしてください。（トークンなし・不正・期限切れ、無効化／削除されたユーザー、パスワード変更前に発行されたトークン）</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
           <t>SCR-001／全画面（認証切れ）</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>ログインは不存在・無効（INACTIVE）・パスワード不一致を同一文言にする。認証切れは画面がトークンを破棄して SCR-001 へ戻す</t>
         </is>
       </c>
     </row>
@@ -894,12 +976,22 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>{項目名}は必須入力です。／新しいパスワードのポリシー違反時はポリシー別の文言（12文字以上、英字と数字を両方含む、現在のパスワードと異なる）</t>
+          <t>入力チェックの項目別メッセージ（例：{項目名}は必須入力です。／…文字以内で入力してください。など。一覧は「入力チェックメッセージ」シート）／入力内容が正しくありません。（JSON 不正・本文欠落・パス／クエリの型不一致・必須クエリ欠落）</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
           <t>全画面，SCR-007（パスワードポリシー違反）</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Bean Validation（fieldErrors に項目別）・Service の検証。パスワードポリシー違反は「新しいパスワードは12文字以上で入力してください。」「…半角の英字と数字を両方含めてください。」「…現在のパスワードと異なるものにしてください。」「…長すぎます（半角で72文字以内にしてください）。」。管理者が設定する初期・再設定パスワードにも同じ検査を行い、同じ文言（「新しいパスワードは…」）を返す</t>
         </is>
       </c>
     </row>
@@ -916,12 +1008,22 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>開始日は終了日以前の日付を指定してください。</t>
+          <t>開始日は終了日以前の日付を指定してください。／対象日は本日以前の日付を指定してください。／修正後の退勤時刻は出勤時刻より後の時刻を指定してください。／付与日数は0より大きい値（0.1〜99.9）で入力してください。／対象日に出勤打刻がないため、休憩・離席を修正できません。／終了時刻は開始時刻より後の時刻を指定してください。／休憩・離席の時刻は出勤 {HH:mm} 以降（退勤済みは 出勤 {HH:mm}〜退勤 {HH:mm}）の範囲内で指定してください。</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>SCR-105</t>
+          <t>SCR-104, SCR-105, SCR-106, SCR-109, SCR-305</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>項目間の整合・範囲の不正。休憩・離席修正申請は提出時・最終承認時の両方で、出勤打刻の有無・開始と終了の前後・出勤〜退勤の範囲を検査する（対象日が未来日の場合は「対象日は本日以前の日付を指定してください。」）</t>
         </is>
       </c>
     </row>
@@ -943,7 +1045,17 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>SCR-105, SCR-106</t>
+          <t>SCR-105, SCR-106, SCR-202, SCR-305</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>提出時の残日数（承認待ち分を引当）不足／最終承認時の消化不足／付与日数の調整で消化済み日数を下回る場合</t>
         </is>
       </c>
     </row>
@@ -960,12 +1072,22 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>同一期間に既に申請があります。</t>
+          <t>同一期間に既に申請があります。／他の休憩・離席の時間帯と重なっています。</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>SCR-105, SCR-106</t>
+          <t>SCR-105, SCR-106, SCR-109</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>休暇：承認待ち・承認済みと期間重複（同日の午前＋午後半休は除く）／打刻修正：同じ対象日の承認待ちあり／休憩・離席修正：同じ対象日・同じ種別の承認待ちあり（「同一期間に既に申請があります。」）、または既存の休憩・離席の区間と時間帯が重なる（「他の休憩・離席の時間帯と重なっています。」。提出時・最終承認時）</t>
         </is>
       </c>
     </row>
@@ -990,6 +1112,16 @@
           <t>SCR-102</t>
         </is>
       </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>出勤・退勤とも二重打刻。退勤済みの日の休憩・離席の打刻にも同じ文言</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -1004,12 +1136,22 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>出勤打刻がないため、退勤打刻できません。</t>
+          <t>出勤打刻がないため、退勤打刻できません。／出勤打刻がないため、休憩・離席の打刻はできません。</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
           <t>SCR-102</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>退勤打刻と、休憩・離席の開始・終了打刻（API-024・025）で文言が異なる</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1173,17 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>SCR-202</t>
+          <t>SCR-201, SCR-202</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>空白のみ（全角含む）も未入力扱い</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1205,17 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>SCR-202</t>
+          <t>SCR-201, SCR-202</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>差戻し・却下にも適用</t>
         </is>
       </c>
     </row>
@@ -1078,6 +1240,16 @@
           <t>全画面</t>
         </is>
       </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>ロール不足（@PreAuthorize／/api/admin/**）、他人の申請・通知（不存在と区別しない）、自分自身の無効化・ロール降格（SCR-302）</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -1097,7 +1269,17 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>SCR-202</t>
+          <t>SCR-106, SCR-201, SCR-202</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>承認・差戻し・却下・取下げの競合、または対象がすでに処理済み</t>
         </is>
       </c>
     </row>
@@ -1122,356 +1304,966 @@
           <t>全画面</t>
         </is>
       </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>想定外の例外（詳細はログのみ）。サーバーに接続できない場合は画面が「サーバーに接続できません。」を表示（E-012 扱い）</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>E-013</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>{項目名}は既に登録されています。</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>{項目名}は既に登録されています。（項目名：メールアドレス／名称／日付）／付与は既に登録されています。</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>SCR-302〜305（重複）</t>
         </is>
       </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>ユーザーのメール、休暇種別の名称、祝日の日付、同一従業員・種別・付与日の付与</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>E-014</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>{項目名}の指定が正しくありません。</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>SCR-302, 305</t>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>{項目名}の指定が正しくありません。（項目名：所属／上長／従業員／休暇種別／付与日）</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>SCR-302, SCR-305</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>存在しない所属、上長に指定できないユーザー（無効・ロール不可・自分自身・循環）、無効な従業員、UNLIMITED／無効の休暇種別、入社日前・未来日・2 年超過去の付与日</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>E-015</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>対象のデータが見つかりません。</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>SCR-106, SCR-302〜305</t>
         </is>
       </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>対象 ID なし、存在しない URL</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>E-016</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>{理由}ため、この操作は行えません。</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>SCR-106, SCR-302, 303</t>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>{理由}ため、この操作は行えません。（理由：申請が下書き・差戻し以外の状態である／年次有給休暇の名称・有給区分・日数ルール・有効フラグは固定である／有効な部下が設定されている）</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>SCR-106, SCR-302, SCR-303</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>実装の全文は各メッセージ参照：「申請が下書き・差戻し以外の状態であるため、この操作は行えません。」「年次有給休暇の名称・有給区分・日数ルール・有効フラグは固定のため、この操作は行えません。」「有効な部下が設定されているため、この操作は行えません。」</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>E-017</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>アカウントがロックされています。しばらくしてから再度お試しください。（HTTP 423。ログイン失敗が 5 回続くと 30 分ロック）</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>SCR-001</t>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>アカウントがロックされています。しばらくしてから再度お試しください。</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>SCR-001, SCR-007</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>ログイン失敗 5 回で 30 分ロック。ロック中はパスワードが正しくても拒否（パスワード変更 API も同様）</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>E-018</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>現在のパスワードが正しくありません。（HTTP 400）</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>現在のパスワードが正しくありません。</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>SCR-007</t>
         </is>
       </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>不一致は失敗回数に加算し、5 回でロック（E-017）</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>E-019</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>初期パスワードのままです。先にパスワードを変更してください。</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>全画面（SCR-007 以外）</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>mustChangePassword（トークンの mcp クレーム）が true の間、/api/auth/password 以外の API を拒否。画面はルーターガードで SCR-007 へ誘導</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>E-020</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>既に休憩中または離席中です。先に終了してください。</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>SCR-102</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>休憩・離席の開始時、開始中（終了していない）の区間が既にある場合。1 勤務日に開始中の区間は 1 つだけ（DB の部分ユニーク索引 uq_attendance_breaks_open でも保証し、同時操作は E-020 に変換）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>E-021</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>休憩中・離席中ではありません。</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>SCR-102</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>休憩・離席の終了時に開始中の区間がない場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>E-022</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>休憩中・離席中は退勤できません。先に休憩（離席）を終了してください。</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>SCR-102</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>退勤打刻時に開始中の区間がある場合（退勤時刻より後に終わる区間を作らないため）。画面は開始中の間、退勤ボタンを無効化する</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>W-001</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>申請を提出します。よろしいですか。</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>SCR-104, SCR-105, SCR-106</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>現行実装は提出前の確認ダイアログなし（「申請する」「提出する」で即実行）。確認ダイアログは未実装</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>W-002</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>申請を取り下げます。よろしいですか。</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>申請を取り下げますか？（取り下げた申請は元に戻せません。）</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>SCR-106</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>実装の確認ダイアログ文言</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>W-003</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>承認しますか？</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>SCR-201, SCR-202</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>コメント任意（500 文字以内）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>W-004</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>差戻しますか？</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>SCR-201, SCR-202</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>コメント必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>W-005</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>却下しますか？</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>SCR-201, SCR-202</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>コメント必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>W-006</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>「{氏名}」を無効化します。無効化したユーザーはログインできなくなります。よろしいですか？</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>SCR-302</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>変更画面から状態を「無効」で保存する場合は「状態を「無効」にして保存します。無効化したユーザーはログインできなくなります。よろしいですか？」</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>W-007</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>{日付}（{名称}）を削除します。よろしいですか？</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>SCR-304</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>祝日・会社休日の削除</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>I-001</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>情報</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>出勤を記録しました。</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>出勤を記録しました（{HH:mm}）。</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>SCR-102</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>I-002</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>情報</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>退勤を記録しました。</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>退勤を記録しました（{HH:mm}／勤務 {H:mm}）。</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>SCR-102</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>I-003</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>情報</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>申請を提出しました。</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>SCR-104, SCR-105, SCR-106</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>新規申請の「申請する」は申請詳細へ遷移（メッセージなし）。SCR-106 の「提出する」で表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>I-004</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>情報</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>承認しました。</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>SCR-202</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>承認しました。（承認待ち一覧では「{氏名} さんの申請を承認しました。」）</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>SCR-201, SCR-202</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>I-005</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>情報</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>差戻ししました。</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>SCR-202</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>差戻しました。（承認待ち一覧では「{氏名} さんの申請を差戻しました。」）</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>SCR-201, SCR-202</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>I-006</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>情報</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>却下しました。</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>SCR-202</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>却下しました。（承認待ち一覧では「{氏名} さんの申請を却下しました。」）</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>SCR-201, SCR-202</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>I-007</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>情報</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>申請を取り下げました。</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>SCR-106</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>I-008</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>情報</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>パスワードを変更しました。</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>SCR-007</t>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>パスワードを変更しました。新しいパスワードでログインしてください。</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>SCR-001（SCR-007 からの遷移後）</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>変更成功後はトークンを破棄して SCR-001 へ遷移し、ログイン画面に表示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>I-009</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>情報</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>休暇を付与しました。／付与日数を調整しました。</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>SCR-305</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>I-010</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>情報</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>{対象}を登録しました。／{対象}を更新しました。（ユーザー「{氏名}」・休暇種別「{名称}」・祝日の日付）</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>SCR-302, SCR-303, SCR-304</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>I-011</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>情報</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>ユーザー「{氏名}」を無効化しました。／ユーザー「{氏名}」のパスワードを再設定しました。</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>SCR-302</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>I-012</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>情報</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>{日付}（{名称}）を削除しました。</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>SCR-304</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>I-013</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>情報</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>{休憩|離席}を開始しました。終わったら「{休憩|離席}終了」を押してください。</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>SCR-102</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>休憩・離席の開始打刻の成功時（画面のメッセージ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>I-014</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>情報</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>{休憩|離席}を終了しました。</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>SCR-102</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>休憩・離席の終了打刻の成功時（画面のメッセージ）</t>
         </is>
       </c>
     </row>
@@ -1479,4 +2271,831 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>※E-002（HTTP 400）の項目別メッセージ。Bean Validation（DTO）と Service の検証メッセージを実装から転記。fieldErrors にはフィールド名とメッセージが入る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>メッセージ</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>条件</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>POST /api/auth/login</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>メールアドレスは必須入力です。／メールアドレスは255文字以内で入力してください。</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>必須（空白のみ不可）・255 文字以内</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>POST /api/auth/login</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>パスワードは必須入力です。</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>POST /api/auth/password</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>currentPassword</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>現在のパスワードは必須入力です。</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>POST /api/auth/password</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>newPassword</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>新しいパスワードは必須入力です。／新しいパスワードは128文字以内で入力してください。</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>必須・128 文字以内。ポリシー検査（Service）は E-002 の個別文言を参照</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>POST /api/auth/password</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>newPassword（ポリシー）</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>新しいパスワードは12文字以上で入力してください。／新しいパスワードが長すぎます（半角で72文字以内にしてください）。／新しいパスワードは半角の英字と数字を両方含めてください。／新しいパスワードは現在のパスワードと異なるものにしてください。</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>12 文字以上・UTF-8 で 72 バイト以内・半角英字と半角数字を両方含む・現在と異なる</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>POST /api/attendance/break-start</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>種別は必須入力です。／種別が正しくありません。</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>必須。BREAK | AWAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>GET /api/attendance</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>対象月は必須入力です。／対象月は yyyy-MM 形式で入力してください。／対象月に未来の月は指定できません。</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>必須・形式・未来月不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>POST /api/requests</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>requestType</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>申請種別は必須入力です。／申請種別が正しくありません。</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>LEAVE | CLOCK_CORRECTION | BREAK_CORRECTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>POST /api/requests</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>取得単位が正しくありません。／取得単位は必須入力です。</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>FULL | AM | PM（休暇は必須）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>POST /api/requests</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>correctedClockIn / correctedClockOut</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>修正後の出勤時刻の形式が正しくありません。／修正後の退勤時刻の形式が正しくありません。／修正後の出勤時刻は必須入力です。／修正後の退勤時刻は必須入力です。</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>HH:mm 形式。打刻修正は出勤・退勤の両方が必須（API）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>POST /api/requests</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>breakKind / breakStart / breakEnd</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>休憩・離席の種別が正しくありません。／休憩・離席の開始時刻の形式が正しくありません。／休憩・離席の終了時刻の形式が正しくありません。／休憩・離席の種別は必須入力です。／開始時刻は必須入力です。／終了時刻は必須入力です。</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>休憩・離席修正申請（BREAK_CORRECTION）。breakKind は BREAK | AWAY、時刻は HH:mm。種別・開始・終了は必須（Service）。時刻の前後・範囲・重複は E-003 / E-005</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>POST /api/requests</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>理由は200文字以内で入力してください。／理由は必須入力です。</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>200 文字以内。打刻修正は提出時に必須（下書きは不要）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>POST /api/requests</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>startDate / endDate / leaveTypeId</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>開始日は必須入力です。／対象日は必須入力です。／休暇種別は必須入力です。／終了日は必須入力です。／期間は1,100日以内で指定してください。／半休は開始日と終了日に同じ日付を指定してください。／休暇種別が正しくありません。／この休暇種別では半日単位を指定できません。／指定期間に取得できる営業日がありません。</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Service（validateInput・create）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>POST /api/requests/{id}/submit</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>（下書きの再検証）</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>理由は必須入力です。／修正後の出勤・退勤時刻は必須入力です。／休暇種別が正しくありません。／この休暇種別では半日単位を指定できません。／指定期間に取得できる営業日がありません。</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>提出時に保存内容を再検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>GET /api/requests</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>状態の指定が正しくありません。</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>6 値以外</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>POST /api/approvals/{stepId}/(approve|return|reject)</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>コメントは500文字以内で入力してください。</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>500 文字以内。差戻し・却下の必須判定は E-008</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>GET /api/approvals/pending</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>requestType / stepNo</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>入力内容が正しくありません。</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>requestType は LEAVE|CLOCK_CORRECTION|BREAK_CORRECTION、stepNo は 1|2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>POST /api/admin/users</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>氏名は必須入力です。／氏名は100文字以内で入力してください。</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>必須・100 文字以内</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>POST・PUT /api/admin/users</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>メールアドレスは必須入力です。／メールアドレスは255文字以内で入力してください。／メールアドレスの形式が正しくありません。</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>必須・255 文字以内・メール形式</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>POST /api/admin/users</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>initialPassword</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>初期パスワードは必須入力です。／初期パスワードは12文字以上72文字以内で入力してください。／初期パスワードは半角英数字・記号で入力してください。／新しいパスワードは半角の英字と数字を両方含めてください。</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>12〜72 文字・半角（0x21〜0x7E）。Service が本人変更と同じポリシー（英字と数字の両方を含む・UTF-8 で 72 バイト以内）を検査し、違反は E-002（文言は「新しいパスワードは…」）。本人は初回ログイン後に変更が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>PUT /api/admin/users/{id}/password</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>newPassword</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>新しいパスワードは必須入力です。／新しいパスワードは12文字以上72文字以内で入力してください。／新しいパスワードは半角英数字・記号で入力してください。／新しいパスワードは半角の英字と数字を両方含めてください。</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>POST・PUT /api/admin/users</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>role / status / hireDate</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>ロールは必須入力です。／ロールの指定が正しくありません。／状態は必須入力です。／状態の指定が正しくありません。／入社日は必須入力です。</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>role: EMPLOYEE|MANAGER|ADMIN、status: ACTIVE|INACTIVE（PUT のみ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>GET /api/admin/users（一覧検索）</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>keyword / role / status</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>検索キーワードは100文字以内で入力してください。／ロールの指定が正しくありません。／状態の指定が正しくありません。</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>GET /api/admin/users のクエリ</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>POST・PUT /api/admin/leave-types</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>name / legalBasis</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>名称は必須入力です。／名称は100文字以内で入力してください。／法的根拠は100文字以内で入力してください。</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>必須・100 文字以内</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>POST・PUT /api/admin/leave-types</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>isPaid / maxDaysRule / allowHalfDay / isActive</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>有給・無給は必須入力です。／日数ルールは必須入力です。／日数ルールの指定が正しくありません。／半日取得可は必須入力です。／有効は必須入力です。</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>maxDaysRule: LIMITED|UNLIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>GET・POST /api/admin/holidays</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>year / holidayDate / name</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>対象年は2000年〜2099年の範囲で指定してください。／日付は2000年〜2099年の範囲で指定してください。／日付は必須入力です。／名称は必須入力です。／名称は100文字以内で入力してください。</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>POST・PUT /api/admin/leave-grants</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>userId / leaveTypeId / grantedOn / grantedDays / note</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>従業員は必須入力です。／休暇種別は必須入力です。／付与日は必須入力です。／付与日数は必須入力です。／調整理由は200文字以内で入力してください。</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>付与日数の範囲は E-003、従業員・種別・付与日の不正は E-014</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>GET /api/admin/reports/monthly・GET /api/manager/subordinates/summary</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>month / format</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>対象月は必須入力です。／対象月はyyyy-MM形式で入力してください。／出力形式はjsonまたはcsvで指定してください。</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>format は管理者の月次集計のみ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>※サーバーのエラーコードを持たない、画面（Vue）側で表示するメッセージ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>メッセージ</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>SCR-001</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>メールアドレスとパスワードを入力してください。</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>ログイン前の未入力チェック（API 呼出し前）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>SCR-007</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>すべての項目を入力してください。／新しいパスワードが一致しません。</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>現在・新しいパスワード未入力、確認入力の不一致（API 呼出し前）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>SCR-104, SCR-105, SCR-109</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>休暇種別を選択してください。／開始日を入力してください。／対象日を入力してください。／修正後の出勤時刻と退勤時刻の両方を入力してください。／開始時刻と終了時刻の両方を入力してください。／理由を入力してください。</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>新規申請フォームの未入力チェック（API 呼出し前）。打刻修正は出勤・退勤の両方が必須（画面・API とも）。「開始時刻と終了時刻の両方を入力してください。」は休憩・離席修正申請（SCR-109）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>SCR-303</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>名称は必須入力です。</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>休暇種別フォームの未入力チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>SCR-304</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>年は1900〜2100の数値で入力してください。</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>年の指定チェック（API の範囲は 2000〜2099）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>SCR-306, SCR-203</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>対象月を選択してください。／対象月を選んで集計してください。／CSVのダウンロードに失敗しました。</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>月の未選択、CSV ダウンロード失敗</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>全画面（API クライアント）</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>サーバーに接続できません。／エラーが発生しました。</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>通信失敗（E-012 扱い）／本文なしのエラー応答</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
 </file>